--- a/workspace/sheets/fx_rates.xlsx
+++ b/workspace/sheets/fx_rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -459,14 +459,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>7.79</v>
       </c>
       <c r="C2" t="n">
-        <v>1.074</v>
+        <v>1.093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -477,14 +477,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>7.78</v>
       </c>
       <c r="C3" t="n">
-        <v>1.071</v>
+        <v>1.09</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -495,14 +495,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>7.79</v>
       </c>
       <c r="C4" t="n">
-        <v>1.072</v>
+        <v>1.074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -513,14 +513,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.81</v>
+        <v>7.78</v>
       </c>
       <c r="C5" t="n">
-        <v>1.077</v>
+        <v>1.071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -531,14 +531,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.82</v>
+        <v>7.79</v>
       </c>
       <c r="C6" t="n">
-        <v>1.079</v>
+        <v>1.072</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -549,14 +549,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.8</v>
+        <v>7.81</v>
       </c>
       <c r="C7" t="n">
-        <v>1.076</v>
+        <v>1.077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -567,14 +567,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.79</v>
+        <v>7.82</v>
       </c>
       <c r="C8" t="n">
-        <v>1.073</v>
+        <v>1.079</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -585,14 +585,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.81</v>
+        <v>7.8</v>
       </c>
       <c r="C9" t="n">
-        <v>1.078</v>
+        <v>1.076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -603,14 +603,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7.82</v>
+        <v>7.79</v>
       </c>
       <c r="C10" t="n">
-        <v>1.083</v>
+        <v>1.073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -621,14 +621,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>7.81</v>
       </c>
       <c r="C11" t="n">
-        <v>1.082</v>
+        <v>1.078</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -639,14 +639,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7.8</v>
+        <v>7.82</v>
       </c>
       <c r="C12" t="n">
-        <v>1.08</v>
+        <v>1.083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -657,16 +657,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Month-start rate, Victoria Harbour Bank board rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Month-start rate, Victoria Harbour Bank board rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B15" t="n">
         <v>7.8</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C15" t="n">
         <v>1.08</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Month-start rate, Victoria Harbour Bank board rate</t>
         </is>
